--- a/Homework/4_Measurements/USDA Soil Texture/Sample 1.1.xlsx
+++ b/Homework/4_Measurements/USDA Soil Texture/Sample 1.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailarizona-my.sharepoint.com/personal/jeffreycarvalho_arizona_edu/Documents/HWRS 563B Measurements/3_Day/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="8_{58AE1647-EE8E-47CF-801C-2267FB2CC5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{542CF1D5-5249-4DDA-BCEA-B999F308F46D}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="8_{58AE1647-EE8E-47CF-801C-2267FB2CC5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{600262C9-6D18-4A46-A86F-0511E80C13BA}"/>
   <bookViews>
-    <workbookView xWindow="55170" yWindow="5850" windowWidth="19875" windowHeight="15345" xr2:uid="{7ECD7FC4-DDEF-4DAA-A193-EAE77382D94C}"/>
+    <workbookView xWindow="25110" yWindow="4665" windowWidth="28800" windowHeight="15285" xr2:uid="{7ECD7FC4-DDEF-4DAA-A193-EAE77382D94C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="31">
   <si>
     <t>SampleName</t>
   </si>
@@ -80,40 +80,55 @@
     <t>Source</t>
   </si>
   <si>
-    <t>Lab</t>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>F1.1</t>
-  </si>
-  <si>
-    <t>F1.2</t>
-  </si>
-  <si>
-    <t>F1.3</t>
-  </si>
-  <si>
-    <t>F1.4</t>
-  </si>
-  <si>
-    <t>F1.5</t>
-  </si>
-  <si>
-    <t>L1.1</t>
-  </si>
-  <si>
-    <t>L1.2</t>
-  </si>
-  <si>
-    <t>L1.3</t>
-  </si>
-  <si>
-    <t>L1.4</t>
-  </si>
-  <si>
-    <t>L1.5</t>
+    <t>Trench Pit 1</t>
+  </si>
+  <si>
+    <t>Trench Pit 2</t>
+  </si>
+  <si>
+    <t>T.1.1</t>
+  </si>
+  <si>
+    <t>T.1.2</t>
+  </si>
+  <si>
+    <t>T.1.3</t>
+  </si>
+  <si>
+    <t>T.1.4</t>
+  </si>
+  <si>
+    <t>T.1.5</t>
+  </si>
+  <si>
+    <t>T.2.1</t>
+  </si>
+  <si>
+    <t>T.2.2</t>
+  </si>
+  <si>
+    <t>T.2.4</t>
+  </si>
+  <si>
+    <t>T.2.5</t>
+  </si>
+  <si>
+    <t>T.2.6</t>
+  </si>
+  <si>
+    <t>T.2.7</t>
+  </si>
+  <si>
+    <t>T.2.8</t>
+  </si>
+  <si>
+    <t>T.2.9</t>
+  </si>
+  <si>
+    <t>T.2.3.5</t>
+  </si>
+  <si>
+    <t>T.2.3</t>
   </si>
 </sst>
 </file>
@@ -503,10 +518,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F2FDD37-B1BB-4F82-8AFF-ADFC7B9895C6}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="1" max="1" width="11.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="10.140625" customWidth="1"/>
     <col min="4" max="4" width="8.140625" customWidth="1"/>
@@ -719,14 +734,14 @@
       <c r="C7" s="1">
         <v>1</v>
       </c>
-      <c r="D7" s="1">
-        <v>60</v>
-      </c>
-      <c r="E7" s="1">
-        <v>30</v>
-      </c>
-      <c r="F7" s="1">
-        <v>10</v>
+      <c r="D7" s="2">
+        <v>95</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>4</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
@@ -752,14 +767,14 @@
       <c r="C8" s="1">
         <v>2</v>
       </c>
-      <c r="D8" s="1">
-        <v>70</v>
-      </c>
-      <c r="E8" s="1">
-        <v>20</v>
-      </c>
-      <c r="F8" s="1">
-        <v>10</v>
+      <c r="D8" s="2">
+        <v>97</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>2</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -778,19 +793,19 @@
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1">
         <v>3</v>
       </c>
-      <c r="D9" s="1">
-        <v>75</v>
-      </c>
-      <c r="E9" s="1">
-        <v>15</v>
-      </c>
-      <c r="F9" s="1">
-        <v>10</v>
+      <c r="D9" s="2">
+        <v>97</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -809,19 +824,19 @@
         <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="D10" s="2">
+        <v>95</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
         <v>4</v>
-      </c>
-      <c r="D10" s="1">
-        <v>70</v>
-      </c>
-      <c r="E10" s="1">
-        <v>15</v>
-      </c>
-      <c r="F10" s="1">
-        <v>15</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -838,19 +853,19 @@
         <v>15</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C11" s="1">
-        <v>5</v>
-      </c>
-      <c r="D11" s="1">
-        <v>65</v>
-      </c>
-      <c r="E11" s="1">
-        <v>20</v>
-      </c>
-      <c r="F11" s="1">
-        <v>15</v>
+        <v>4</v>
+      </c>
+      <c r="D11" s="2">
+        <v>14</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>85</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -863,11 +878,24 @@
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="1">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2">
+        <v>90</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>9</v>
+      </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -876,6 +904,86 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="1">
+        <v>6</v>
+      </c>
+      <c r="D13" s="2">
+        <v>90</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="1">
+        <v>7</v>
+      </c>
+      <c r="D14" s="2">
+        <v>50</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="1">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2">
+        <v>20</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="1">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2">
+        <v>10</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
